--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104629_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104629_W19.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7099</v>
+        <v>6.0046</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2776</v>
+        <v>7.372</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5677</v>
+        <v>-1.3674</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1482</v>
+        <v>5.1593</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4963</v>
+        <v>5.4905</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8175</v>
+        <v>6.794</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5585</v>
+        <v>1.5513</v>
       </c>
       <c r="L2" t="n">
-        <v>5.259</v>
+        <v>5.2427</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6692</v>
+        <v>-1.6348</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9065</v>
+        <v>-1.8825</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2253</v>
+        <v>0.5007</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2994</v>
+        <v>0.4202</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0741</v>
+        <v>0.0805</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.081</v>
+        <v>2.7483</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7369</v>
+        <v>4.3433</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6559</v>
+        <v>-1.5951</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7637</v>
+        <v>4.754</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3189</v>
+        <v>-1.3156</v>
       </c>
       <c r="I3" t="n">
-        <v>6.0826</v>
+        <v>6.0696</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6362</v>
+        <v>6.6036</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L3" t="n">
-        <v>6.7889</v>
+        <v>6.7694</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8725</v>
+        <v>-1.8496</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1364</v>
+        <v>-0.461</v>
       </c>
       <c r="T3" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5054</v>
+        <v>-0.4771</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8925</v>
+        <v>2.6427</v>
       </c>
       <c r="E4" t="n">
-        <v>3.96</v>
+        <v>3.4594</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0675</v>
+        <v>-0.8167</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5263</v>
+        <v>1.5359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7026</v>
+        <v>0.7091</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8237</v>
+        <v>0.8269</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5829</v>
+        <v>3.5711</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0566</v>
+        <v>-2.0351</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.114</v>
+        <v>-0.3681</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2994</v>
+        <v>-0.1721</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4134</v>
+        <v>-0.1961</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3625</v>
+        <v>1.3695</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5469</v>
+        <v>1.6564</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1844</v>
+        <v>-0.2869</v>
       </c>
       <c r="G5" t="n">
-        <v>1.02</v>
+        <v>1.0305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0764</v>
+        <v>0.0829</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5949</v>
+        <v>1.5893</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5749</v>
+        <v>-0.5588</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3133</v>
+        <v>-0.3227</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1047</v>
+        <v>-0.232</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.31</v>
+        <v>0.5319</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5049</v>
+        <v>1.3551</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.195</v>
+        <v>-0.8232</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4036</v>
+        <v>2.4027</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8269</v>
+        <v>-0.819</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2305</v>
+        <v>3.2216</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4043</v>
+        <v>3.3784</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7187</v>
+        <v>2.703</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0007</v>
+        <v>-0.9758</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5125</v>
+        <v>-1.4945</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1183</v>
+        <v>0.1081</v>
       </c>
       <c r="T6" t="n">
-        <v>0.369</v>
+        <v>0.253</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4872</v>
+        <v>-0.1449</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2495</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0537</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8042</v>
+        <v>0.0733</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5829</v>
+        <v>-0.344</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8095</v>
+        <v>-0.3247</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2266</v>
+        <v>-0.0193</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0008</v>
+        <v>0.0717</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1874</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1866</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5821</v>
+        <v>-0.4157</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6221</v>
+        <v>-0.3592</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04</v>
+        <v>-0.0565</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4606</v>
+        <v>-0.4912</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5081</v>
+        <v>-0.0697</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9687</v>
+        <v>-0.4215</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0379</v>
+        <v>-0.1227</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0024</v>
+        <v>0.5676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0355</v>
+        <v>-0.6904</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3489</v>
+        <v>-1.5783</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3276</v>
+        <v>-1.8094</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0213</v>
+        <v>0.2311</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.0142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>-0.2003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.1862</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4209</v>
+        <v>-1.5642</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3622</v>
+        <v>-1.6091</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0586</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5205</v>
+        <v>-0.8419</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0696</v>
+        <v>0.037</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4509</v>
+        <v>-0.879</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4751</v>
+        <v>-0.7307</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0852</v>
+        <v>0.0444</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5603</v>
+        <v>-0.7751</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5807</v>
+        <v>0.5841</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7778</v>
+        <v>0.7729</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1972</v>
+        <v>-0.1888</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2362</v>
+        <v>3.2085</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8257</v>
+        <v>2.7989</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4105</v>
+        <v>0.4096</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6556</v>
+        <v>-2.6244</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5982</v>
+        <v>0.3485</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>0.0926</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5075</v>
+        <v>0.2559</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.975</v>
+        <v>-1.5649</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1238</v>
+        <v>0.298</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1488</v>
+        <v>-1.8628</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.681</v>
+        <v>3.2957</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6654</v>
+        <v>-1.0547</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0156</v>
+        <v>4.3504</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3471</v>
+        <v>5.4607</v>
       </c>
       <c r="K10" t="n">
-        <v>0.218</v>
+        <v>0.9858</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5652</v>
+        <v>4.475</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3338</v>
+        <v>-2.1651</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8834</v>
+        <v>-2.0405</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4504</v>
+        <v>-0.1246</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-5.6908</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7455000000000001</v>
+        <v>-0.0591</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.1745</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4411</v>
+        <v>0.1154</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3214</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3214</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1027</v>
+        <v>-1.8495</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2272</v>
+        <v>-3.5675</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8755</v>
+        <v>1.718</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3021</v>
+        <v>-1.667</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0665</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3687</v>
+        <v>-1.0144</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5018</v>
+        <v>-0.3638</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9973</v>
+        <v>0.2101</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5045</v>
+        <v>-0.5739</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1996</v>
+        <v>-1.3032</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0638</v>
+        <v>-0.8628</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1359</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8562</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6708</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6167</v>
+        <v>0.8678</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7652</v>
+        <v>-0.1048</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1485</v>
+        <v>0.9726</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.3155</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7071</v>
+        <v>0.3155</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.090499999999999</v>
+        <v>9.104500000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>15.8166</v>
+        <v>15.5307</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.7262</v>
+        <v>-6.426299999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>15.1318</v>
+        <v>15.1729</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.806</v>
+        <v>-4.7424</v>
       </c>
       <c r="I12" t="n">
-        <v>19.9379</v>
+        <v>19.9152</v>
       </c>
       <c r="J12" t="n">
-        <v>30.4979</v>
+        <v>30.2993</v>
       </c>
       <c r="K12" t="n">
-        <v>8.5078</v>
+        <v>8.406500000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>21.9898</v>
+        <v>21.893</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.3659</v>
+        <v>-15.1267</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.3138</v>
+        <v>-13.1489</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.052</v>
+        <v>-1.9779</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.402699999999999</v>
+        <v>-3.4146</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.2807</v>
+        <v>-19.3487</v>
       </c>
       <c r="R12" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7108</v>
+        <v>-0.7189</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1965</v>
+        <v>0.2071</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9073000000000001</v>
+        <v>-0.9261999999999998</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.928199999999999</v>
+        <v>-1.9349</v>
       </c>
       <c r="W12" t="n">
-        <v>4.403</v>
+        <v>4.3728</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.3312</v>
+        <v>-6.3077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.288</v>
+        <v>1.3544</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5158</v>
+        <v>4.6502</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2278</v>
+        <v>-3.2958</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4216</v>
+        <v>1.0029</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1141</v>
+        <v>4.1564</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5357</v>
+        <v>-3.1535</v>
       </c>
       <c r="J13" t="n">
-        <v>1.425</v>
+        <v>5.3432</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1936</v>
+        <v>5.2917</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2315</v>
+        <v>0.0515</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8467</v>
+        <v>-4.3403</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0795</v>
+        <v>-1.1353</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7672</v>
+        <v>-3.205</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1918</v>
+        <v>-0.3997</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4517</v>
+        <v>0.1297</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7401</v>
+        <v>-0.5294</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4822</v>
+        <v>-0.387</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4822</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1137</v>
+        <v>1.0739</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7711</v>
+        <v>1.746</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6574</v>
+        <v>-0.672</v>
       </c>
       <c r="G14" t="n">
-        <v>0.792</v>
+        <v>0.7893</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6769</v>
+        <v>1.6664</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8849</v>
+        <v>-0.877</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2814</v>
+        <v>2.264</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2441</v>
+        <v>2.2268</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7709</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4688</v>
+        <v>-0.4694</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9104</v>
+        <v>0.3712</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9514</v>
+        <v>0.7896</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.041</v>
+        <v>-0.4185</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3401</v>
+        <v>-0.4249</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3143</v>
+        <v>0.1067</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0258</v>
+        <v>-0.5316</v>
       </c>
       <c r="J15" t="n">
-        <v>2.27</v>
+        <v>1.4077</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.1789</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4499</v>
+        <v>1.2288</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.6101</v>
+        <v>-1.8326</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1344</v>
+        <v>-0.0722</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.4758</v>
+        <v>-1.7604</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4025</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3847</v>
+        <v>1.2694</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5375</v>
+        <v>0.7477</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8471</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>-0.4733</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3135</v>
+        <v>0.1426</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4291</v>
+        <v>-0.4643</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7426</v>
+        <v>0.607</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4264</v>
+        <v>-2.4395</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3229</v>
+        <v>-1.3403</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8778</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.9523</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5721</v>
+        <v>-1.5617</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0348</v>
+        <v>-0.122</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3992</v>
+        <v>-0.3997</v>
       </c>
       <c r="U16" t="n">
-        <v>0.434</v>
+        <v>0.2777</v>
       </c>
       <c r="V16" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1679</v>
+        <v>0.0017</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7534</v>
+        <v>1.4358</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5855</v>
+        <v>-1.4341</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0126</v>
+        <v>-2.5394</v>
       </c>
       <c r="H17" t="n">
-        <v>4.166</v>
+        <v>-0.0485</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1533</v>
+        <v>-2.4909</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3828</v>
+        <v>0.7997</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3162</v>
+        <v>1.5751</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0665</v>
+        <v>-0.7754</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.3701</v>
+        <v>-3.339</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1503</v>
+        <v>-1.6235</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.2198</v>
+        <v>-1.7155</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5933</v>
+        <v>-0.5971</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8166</v>
+        <v>-0.2257</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.3714</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3856</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8279</v>
+        <v>-0.8111</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8883</v>
+        <v>1.8565</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7162</v>
+        <v>-2.6676</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5261</v>
+        <v>-1.6055</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0417</v>
+        <v>0.4309</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.4843</v>
+        <v>-2.0364</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8391</v>
+        <v>1.8613</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5962</v>
+        <v>1.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7572</v>
+        <v>0.8411</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3652</v>
+        <v>-3.4668</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.638</v>
+        <v>-0.5893</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7272</v>
+        <v>-2.8775</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.436</v>
+        <v>0.2693</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8166</v>
+        <v>0.2715</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6194</v>
+        <v>-0.0022</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8833</v>
+        <v>-0.8662</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0036</v>
+        <v>0.4842</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8869</v>
+        <v>-1.3505</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6009</v>
+        <v>-2.3596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4329</v>
+        <v>-0.3322</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0338</v>
+        <v>-2.0274</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8848</v>
+        <v>2.2256</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0319</v>
+        <v>0.7887</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8529</v>
+        <v>1.4369</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4857</v>
+        <v>-4.5852</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.599</v>
+        <v>-1.1209</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.8867</v>
+        <v>-3.4643</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1978</v>
+        <v>1.6316</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3871</v>
+        <v>1.1284</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1893</v>
+        <v>0.5032</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4088</v>
+        <v>-1.019</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8016</v>
+        <v>-0.4503</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6072</v>
+        <v>-0.5687</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.971</v>
+        <v>-1.9701</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1025</v>
+        <v>-0.1006</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8685</v>
+        <v>-1.8695</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6625</v>
+        <v>-0.6662</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3086</v>
+        <v>-1.3039</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1183</v>
+        <v>0.2682</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5102</v>
+        <v>-2.3885</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9179</v>
+        <v>-1.9333</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5923</v>
+        <v>-0.4552</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9544</v>
+        <v>-0.953</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7489</v>
+        <v>0.7496</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7033</v>
+        <v>-1.7026</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4714</v>
+        <v>0.4639</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4258</v>
+        <v>-1.4169</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5513</v>
+        <v>-1.546</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1948</v>
+        <v>-0.0697</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>-0.1209</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1049</v>
+        <v>-2.5698</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4503</v>
+        <v>-2.0047</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6546</v>
+        <v>-0.5651</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5306</v>
+        <v>-0.5233</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1891</v>
+        <v>0.1868</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7196</v>
+        <v>-0.7101</v>
       </c>
       <c r="J22" t="n">
-        <v>1.926</v>
+        <v>1.9118</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2917</v>
+        <v>1.2788</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4566</v>
+        <v>-2.4351</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9866</v>
+        <v>-0.4531</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.149</v>
+        <v>-4.3936</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4412</v>
+        <v>0.3165</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5903</v>
+        <v>-4.7101</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1655</v>
+        <v>-4.1496</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.4251</v>
+        <v>-3.4168</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4019</v>
+        <v>0.3935</v>
       </c>
       <c r="K23" t="n">
-        <v>1.039</v>
+        <v>1.0342</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.5674</v>
+        <v>-4.5431</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7794</v>
+        <v>-1.767</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.788</v>
+        <v>-2.7761</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0015</v>
+        <v>-0.2731</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0393</v>
+        <v>-0.077</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0378</v>
+        <v>-0.1961</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.0906</v>
+        <v>-9.1044</v>
       </c>
       <c r="E24" t="n">
-        <v>6.725900000000001</v>
+        <v>6.4262</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.8166</v>
+        <v>-15.5306</v>
       </c>
       <c r="G24" t="n">
-        <v>-15.132</v>
+        <v>-15.1727</v>
       </c>
       <c r="H24" t="n">
-        <v>4.806100000000001</v>
+        <v>4.7424</v>
       </c>
       <c r="I24" t="n">
-        <v>-19.9378</v>
+        <v>-19.9149</v>
       </c>
       <c r="J24" t="n">
-        <v>15.3656</v>
+        <v>15.1267</v>
       </c>
       <c r="K24" t="n">
-        <v>13.3139</v>
+        <v>13.1488</v>
       </c>
       <c r="L24" t="n">
-        <v>2.0518</v>
+        <v>1.9779</v>
       </c>
       <c r="M24" t="n">
-        <v>-30.49769999999999</v>
+        <v>-30.2993</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.508000000000001</v>
+        <v>-8.406500000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-21.9898</v>
+        <v>-21.893</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4026</v>
+        <v>3.4146</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R24" t="n">
-        <v>19.2808</v>
+        <v>19.3488</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7107000000000003</v>
+        <v>0.7189000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9073</v>
+        <v>0.9261000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1964999999999999</v>
+        <v>-0.2070999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9281</v>
+        <v>1.9348</v>
       </c>
       <c r="W24" t="n">
-        <v>6.3311</v>
+        <v>6.3076</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.4031</v>
+        <v>-4.3728</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104629_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104629_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.3077</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104629_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.3728</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
